--- a/reports/latest_backtest_summary.xlsx
+++ b/reports/latest_backtest_summary.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Full Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backtest Full Results'!$A$8:$I$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backtest Full Results'!$A$8:$I$233</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       <c r="B23" s="8" t="inlineStr"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1237,17 +1237,13 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
+          <t>supertrend_rsi</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1278,13 +1274,17 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>rsi_psar_reversal</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr"/>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1315,13 +1315,17 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>supertrend_rsi</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr"/>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1357,12 +1361,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>EMA5/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1393,17 +1397,17 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>EMA5/13</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1439,12 +1443,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1480,12 +1484,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1521,12 +1525,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1557,17 +1561,17 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>trend_scalp_nw</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1598,17 +1602,17 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1644,12 +1648,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1685,12 +1689,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1726,12 +1730,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1762,17 +1766,17 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1803,17 +1807,17 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1849,12 +1853,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -1885,17 +1889,17 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -1926,17 +1930,17 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -1967,17 +1971,17 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2008,17 +2012,17 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2049,17 +2053,17 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>trend_scalp_nw</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -2090,17 +2094,17 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2131,17 +2135,17 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>trend_scalp_nw</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2172,17 +2176,17 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2213,17 +2217,17 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -2254,17 +2258,17 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2295,17 +2299,17 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -2336,17 +2340,17 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2377,17 +2381,17 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>FINNIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -2418,12 +2422,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -2459,12 +2463,12 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2500,12 +2504,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -2541,14 +2545,10 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
+          <t>mean_reversion</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr"/>
       <c r="C57" s="8" t="inlineStr">
         <is>
           <t>FINNIFTY</t>
@@ -2582,12 +2582,12 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2664,14 +2664,10 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>EMA8/26</t>
-        </is>
-      </c>
+          <t>rsi_psar_reversal</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr"/>
       <c r="C60" s="8" t="inlineStr">
         <is>
           <t>FINNIFTY</t>
@@ -2705,14 +2701,10 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>EMA8/26</t>
-        </is>
-      </c>
+          <t>supertrend_rsi</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr"/>
       <c r="C61" s="8" t="inlineStr">
         <is>
           <t>FINNIFTY</t>
@@ -2746,12 +2738,12 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -2787,12 +2779,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2828,12 +2820,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -2869,12 +2861,12 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2910,12 +2902,12 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -2951,12 +2943,12 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2992,12 +2984,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -3033,12 +3025,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>trend_scalp_nw</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3074,12 +3066,12 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -3115,12 +3107,12 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -3156,12 +3148,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -3197,12 +3189,12 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -3238,12 +3230,12 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -3279,12 +3271,12 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3320,12 +3312,12 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -3361,12 +3353,12 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -3402,12 +3394,12 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -3443,12 +3435,12 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -3484,12 +3476,12 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -3525,12 +3517,12 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_scalp_nw</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -3566,12 +3558,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -3607,12 +3599,12 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -3648,12 +3640,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>ema_price_action</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -3689,12 +3681,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3730,12 +3722,12 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -3771,1365 +3763,1433 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
           <t>trendline_rsi</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>EMA9/26</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>FINNIFTY</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>trendline_rsi</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/13</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H88" s="11" t="n">
-        <v>-38.22</v>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H89" s="11" t="n">
-        <v>-48.12</v>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H90" s="11" t="n">
-        <v>-48.12</v>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/13</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H91" s="11" t="n">
-        <v>-76.47</v>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>trend_pullback</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/13</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="11" t="n">
-        <v>-218.67</v>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>FINNIFTY</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="11" t="n">
-        <v>-287.01</v>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>trend_pullback</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/13</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H94" s="11" t="n">
-        <v>-348.48</v>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/21</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="11" t="n">
-        <v>-790.6900000000001</v>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/26</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F96" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H96" s="11" t="n">
-        <v>-852.39</v>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H97" s="11" t="n">
-        <v>-857.55</v>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>opening_range_breakout</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/13</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H98" s="11" t="n">
-        <v>-996.58</v>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="11" t="n">
-        <v>-1059.81</v>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/26</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H100" s="11" t="n">
-        <v>-1115.73</v>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="11" t="n">
-        <v>-1332.18</v>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/26</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>0.3684000000000001</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H102" s="11" t="n">
-        <v>-1388.42</v>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/26</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H103" s="11" t="n">
-        <v>-1491.96</v>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/26</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="11" t="n">
-        <v>-2025.3</v>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>combo_trend_vwap</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H105" s="11" t="n">
-        <v>-2537.43</v>
-      </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>trendline_rsi</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H106" s="11" t="n">
-        <v>-2601.44</v>
-      </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>vwap_ema_momentum</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/13</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F107" s="6" t="n">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H107" s="11" t="n">
-        <v>-2615.11</v>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H108" s="11" t="n">
-        <v>-2909.83</v>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/26</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F109" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="11" t="n">
-        <v>-3154.61</v>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F110" s="6" t="n">
-        <v>0.1304</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H110" s="11" t="n">
-        <v>-3487.09</v>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>combo_trend_vwap</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F111" s="6" t="n">
-        <v>0.0526</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H111" s="11" t="n">
-        <v>-3861.44</v>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>trendline_rsi</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F112" s="6" t="n">
-        <v>0.1786</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H112" s="11" t="n">
-        <v>-3871.16</v>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>opening_range_breakout</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/13</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F113" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H113" s="11" t="n">
-        <v>-3964.15</v>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>combo_trend_vwap</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F114" s="6" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H114" s="11" t="n">
-        <v>-4331.79</v>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>trendline_rsi</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/21</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>0.1562</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H115" s="11" t="n">
-        <v>-4676.4</v>
-      </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>combo_trend_vwap</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/26</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F116" s="6" t="n">
-        <v>0.1071</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H116" s="11" t="n">
-        <v>-4688.33</v>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/21</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>0.0645</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H117" s="11" t="n">
-        <v>-5831.04</v>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>combo_trend_vwap</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>EMA8/26</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="F118" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H118" s="11" t="n">
-        <v>-6042.84</v>
-      </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>trend_pullback</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="F119" s="6" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H119" s="11" t="n">
-        <v>-6271.89</v>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>vwap_ema_momentum</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>EMA5/13</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F120" s="6" t="n">
-        <v>0.08109999999999999</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H120" s="11" t="n">
-        <v>-6392.71</v>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>ema_price_action</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/26</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>0.0333</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H121" s="11" t="n">
-        <v>-6445.18</v>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -5138,12 +5198,12 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>ema_price_action</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -5157,16 +5217,16 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.5</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>-6626.6</v>
+        <v>-38.22</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -5177,12 +5237,12 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>trend_scalp_nw</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>EMA9/21</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -5196,16 +5256,16 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.1026</v>
+        <v>0.5</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.14</v>
+        <v>0.95</v>
       </c>
       <c r="H123" s="11" t="n">
-        <v>-6740.24</v>
+        <v>-48.12</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
@@ -5216,7 +5276,7 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_scalp_nw</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -5235,16 +5295,16 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.075</v>
+        <v>0.5</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.15</v>
+        <v>0.95</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>-6901.02</v>
+        <v>-48.12</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -5260,7 +5320,7 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -5274,16 +5334,16 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0.0294</v>
+        <v>0.5</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.02</v>
+        <v>0.65</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>-6996.25</v>
+        <v>-76.47</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -5294,12 +5354,12 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -5313,16 +5373,16 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0.07139999999999999</v>
+        <v>0</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>-7182.86</v>
+        <v>-218.67</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -5333,13 +5393,17 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>rsi_psar_reversal</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr"/>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>FINNIFTY</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5348,16 +5412,16 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.0286</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>-7257.67</v>
+        <v>-287.01</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
@@ -5368,17 +5432,17 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5387,16 +5451,16 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H128" s="11" t="n">
-        <v>-7543.9</v>
+        <v>-315.55</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -5407,17 +5471,17 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -5426,16 +5490,16 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0.0698</v>
+        <v>0</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>-7563.03</v>
+        <v>-315.55</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
@@ -5446,17 +5510,17 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -5465,16 +5529,16 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>0.0732</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H130" s="11" t="n">
-        <v>-7759.56</v>
+        <v>-315.55</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -5485,17 +5549,17 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>combo_trend_vwap</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA5/13</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -5504,16 +5568,16 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H131" s="11" t="n">
-        <v>-7814.66</v>
+        <v>-320.39</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -5524,17 +5588,17 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -5543,16 +5607,16 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H132" s="11" t="n">
-        <v>-7902.21</v>
+        <v>-320.39</v>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
@@ -5563,17 +5627,17 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>EMA5/13</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -5582,16 +5646,16 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>-8214.799999999999</v>
+        <v>-320.39</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -5602,17 +5666,17 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>trendline_rsi</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA8/13</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -5621,16 +5685,16 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>-8794.83</v>
+        <v>-320.39</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -5641,17 +5705,17 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA9/13</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -5660,16 +5724,16 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>0.0233</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H135" s="11" t="n">
-        <v>-8853.860000000001</v>
+        <v>-320.39</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -5680,17 +5744,13 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>EMA9/21</t>
-        </is>
-      </c>
+          <t>rsi_psar_reversal</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr"/>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -5699,16 +5759,16 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>-9155.52</v>
+        <v>-322.8</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -5719,17 +5779,17 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>rsi_adx_nw</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -5738,16 +5798,16 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H137" s="11" t="n">
-        <v>-9255.969999999999</v>
+        <v>-324.46</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -5758,17 +5818,17 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -5777,16 +5837,16 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H138" s="11" t="n">
-        <v>-9368.9</v>
+        <v>-325.67</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -5797,7 +5857,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -5807,7 +5867,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5816,16 +5876,16 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H139" s="11" t="n">
-        <v>-9465.809999999999</v>
+        <v>-325.67</v>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
@@ -5841,12 +5901,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -5855,16 +5915,16 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H140" s="11" t="n">
-        <v>-9496.66</v>
+        <v>-325.67</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -5875,17 +5935,17 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5894,16 +5954,16 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H141" s="11" t="n">
-        <v>-9576.43</v>
+        <v>-325.67</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -5914,7 +5974,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -5924,7 +5984,7 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -5933,16 +5993,16 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H142" s="11" t="n">
-        <v>-9603.959999999999</v>
+        <v>-325.67</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -5953,17 +6013,17 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA5/26</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -5972,16 +6032,16 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H143" s="11" t="n">
-        <v>-9633.969999999999</v>
+        <v>-325.67</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -6002,7 +6062,7 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -6011,16 +6071,16 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H144" s="11" t="n">
-        <v>-9740.77</v>
+        <v>-325.67</v>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
@@ -6031,17 +6091,17 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -6050,16 +6110,16 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H145" s="11" t="n">
-        <v>-9832.120000000001</v>
+        <v>-325.67</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -6070,17 +6130,17 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/21</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -6089,16 +6149,16 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H146" s="11" t="n">
-        <v>-9837.9</v>
+        <v>-325.67</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -6109,17 +6169,17 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>trend_pullback</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -6128,16 +6188,16 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H147" s="11" t="n">
-        <v>-9878.370000000001</v>
+        <v>-325.67</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -6148,17 +6208,17 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -6167,16 +6227,16 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>-9945.85</v>
+        <v>-325.67</v>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
@@ -6187,17 +6247,17 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>opening_range_breakout</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA8/26</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -6206,16 +6266,16 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>0.0204</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H149" s="11" t="n">
-        <v>-9979.58</v>
+        <v>-325.67</v>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
@@ -6226,17 +6286,17 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>EMA5/13</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -6245,16 +6305,16 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="H150" s="11" t="n">
-        <v>-10004</v>
+        <v>-325.67</v>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
@@ -6265,17 +6325,17 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>EMA9/26</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6284,16 +6344,16 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H151" s="11" t="n">
-        <v>-10083.78</v>
+        <v>-325.67</v>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
@@ -6304,17 +6364,17 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>EMA8/13</t>
+          <t>EMA9/21</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6323,16 +6383,16 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H152" s="11" t="n">
-        <v>-10114.22</v>
+        <v>-325.67</v>
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
@@ -6343,17 +6403,17 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>opening_range_breakout</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>EMA9/13</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -6362,16 +6422,16 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H153" s="11" t="n">
-        <v>-10114.22</v>
+        <v>-325.67</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
@@ -6382,17 +6442,17 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trend_pullback</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>EMA5/21</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -6401,16 +6461,16 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H154" s="11" t="n">
-        <v>-10118.75</v>
+        <v>-325.67</v>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
@@ -6421,17 +6481,17 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>trendline_rsi</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>EMA5/26</t>
+          <t>EMA9/26</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -6440,16 +6500,16 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H155" s="11" t="n">
-        <v>-10119.26</v>
+        <v>-325.67</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
@@ -6460,17 +6520,17 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>vwap_ema_momentum</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>EMA8/21</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -6479,16 +6539,16 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H156" s="11" t="n">
-        <v>-10119.26</v>
+        <v>-326.73</v>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
@@ -6499,17 +6559,17 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>rsi_adx_nw</t>
+          <t>combo_trend_vwap</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>EMA8/26</t>
+          <t>EMA5/21</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -6518,16 +6578,16 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H157" s="11" t="n">
-        <v>-10119.26</v>
+        <v>-326.73</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
@@ -6538,51 +6598,2972 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="11" t="n">
+        <v>-326.73</v>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="11" t="n">
+        <v>-326.73</v>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="11" t="n">
+        <v>-326.73</v>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="11" t="n">
+        <v>-326.73</v>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="11" t="n">
+        <v>-336.91</v>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H163" s="11" t="n">
+        <v>-348.48</v>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="11" t="n">
+        <v>-691.8099999999999</v>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="11" t="n">
+        <v>-691.8099999999999</v>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="11" t="n">
+        <v>-790.6900000000001</v>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H167" s="11" t="n">
+        <v>-852.39</v>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H168" s="11" t="n">
+        <v>-857.55</v>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F169" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H169" s="11" t="n">
+        <v>-996.58</v>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="11" t="n">
+        <v>-1059.81</v>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F171" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H171" s="11" t="n">
+        <v>-1115.73</v>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F172" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="11" t="n">
+        <v>-1332.18</v>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F173" s="6" t="n">
+        <v>0.3684000000000001</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H173" s="11" t="n">
+        <v>-1388.42</v>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H174" s="11" t="n">
+        <v>-1491.96</v>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F175" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="11" t="n">
+        <v>-1614.72</v>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="11" t="n">
+        <v>-2025.3</v>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F177" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H177" s="11" t="n">
+        <v>-2537.43</v>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F178" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="11" t="n">
+        <v>-2562.92</v>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F179" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H179" s="11" t="n">
+        <v>-2601.44</v>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F180" s="6" t="n">
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H180" s="11" t="n">
+        <v>-2615.11</v>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H181" s="11" t="n">
+        <v>-2909.83</v>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="11" t="n">
+        <v>-2921.78</v>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F183" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="11" t="n">
+        <v>-3154.61</v>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F184" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" s="11" t="n">
+        <v>-3225.15</v>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F185" s="6" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H185" s="11" t="n">
+        <v>-3487.09</v>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F186" s="6" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H186" s="11" t="n">
+        <v>-3861.44</v>
+      </c>
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F187" s="6" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H187" s="11" t="n">
+        <v>-3871.16</v>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F188" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H188" s="11" t="n">
+        <v>-3964.15</v>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F189" s="6" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H189" s="11" t="n">
+        <v>-4331.79</v>
+      </c>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F190" s="6" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H190" s="11" t="n">
+        <v>-4676.4</v>
+      </c>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F191" s="6" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H191" s="11" t="n">
+        <v>-4688.33</v>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F192" s="6" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H192" s="11" t="n">
+        <v>-5831.04</v>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F193" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H193" s="11" t="n">
+        <v>-6042.84</v>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F194" s="6" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H194" s="11" t="n">
+        <v>-6271.89</v>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F195" s="6" t="n">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H195" s="11" t="n">
+        <v>-6392.71</v>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F196" s="6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H196" s="11" t="n">
+        <v>-6445.18</v>
+      </c>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F197" s="6" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H197" s="11" t="n">
+        <v>-6626.6</v>
+      </c>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H198" s="11" t="n">
+        <v>-6740.24</v>
+      </c>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F199" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H199" s="11" t="n">
+        <v>-6901.02</v>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F200" s="6" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H200" s="11" t="n">
+        <v>-6996.25</v>
+      </c>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F201" s="6" t="n">
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H201" s="11" t="n">
+        <v>-7182.86</v>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>rsi_psar_reversal</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr"/>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F202" s="6" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H202" s="11" t="n">
+        <v>-7231.25</v>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F203" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H203" s="11" t="n">
+        <v>-7543.9</v>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F204" s="6" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H204" s="11" t="n">
+        <v>-7563.03</v>
+      </c>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F205" s="6" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H205" s="11" t="n">
+        <v>-7759.56</v>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F206" s="6" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H206" s="11" t="n">
+        <v>-7814.66</v>
+      </c>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F207" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H207" s="11" t="n">
+        <v>-7902.21</v>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F208" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H208" s="11" t="n">
+        <v>-8214.799999999999</v>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H209" s="11" t="n">
+        <v>-8794.83</v>
+      </c>
+      <c r="I209" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H210" s="11" t="n">
+        <v>-8853.860000000001</v>
+      </c>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F211" s="6" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H211" s="11" t="n">
+        <v>-9155.52</v>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F212" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H212" s="11" t="n">
+        <v>-9255.969999999999</v>
+      </c>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F213" s="6" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H213" s="11" t="n">
+        <v>-9368.9</v>
+      </c>
+      <c r="I213" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F214" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H214" s="11" t="n">
+        <v>-9465.809999999999</v>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F215" s="6" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H215" s="11" t="n">
+        <v>-9496.66</v>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F216" s="6" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H216" s="11" t="n">
+        <v>-9576.43</v>
+      </c>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F217" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H217" s="11" t="n">
+        <v>-9603.959999999999</v>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F218" s="6" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H218" s="11" t="n">
+        <v>-9633.969999999999</v>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F219" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H219" s="11" t="n">
+        <v>-9740.77</v>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F220" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H220" s="11" t="n">
+        <v>-9832.120000000001</v>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F221" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H221" s="11" t="n">
+        <v>-9837.9</v>
+      </c>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F222" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H222" s="11" t="n">
+        <v>-9878.370000000001</v>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
           <t>rsi_adx_nw</t>
         </is>
       </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F223" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H223" s="11" t="n">
+        <v>-9938.59</v>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F224" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H224" s="11" t="n">
+        <v>-9945.85</v>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F225" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H225" s="11" t="n">
+        <v>-9950.41</v>
+      </c>
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F226" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H226" s="11" t="n">
+        <v>-9950.41</v>
+      </c>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
         <is>
           <t>EMA9/21</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>NIFTY</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F227" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H227" s="11" t="n">
+        <v>-9950.41</v>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F228" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H228" s="11" t="n">
+        <v>-9979.58</v>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="F229" s="6" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H229" s="11" t="n">
+        <v>-9993.700000000001</v>
+      </c>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F158" s="6" t="n">
+      <c r="F230" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="G158" s="5" t="n">
+      <c r="G230" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="H158" s="11" t="n">
-        <v>-10119.26</v>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
+      <c r="H230" s="11" t="n">
+        <v>-10094.35</v>
+      </c>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F231" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H231" s="11" t="n">
+        <v>-10094.35</v>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F232" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H232" s="11" t="n">
+        <v>-10118.27</v>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F233" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H233" s="11" t="n">
+        <v>-10124.56</v>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="12" t="inlineStr">
         <is>
           <t>Note: small sample sizes (1-4 trades) don't prove a real edge yet. Grey rows = zero trades. Click the filter arrows on the header row to sort/filter.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:I158"/>
+  <autoFilter ref="A8:I233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_backtest_summary.xlsx
+++ b/reports/latest_backtest_summary.xlsx
@@ -9,15 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Full Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backtest Full Results'!$A$8:$I$83</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;+Rs&quot;#,##0.00;&quot;-Rs&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +49,21 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000B8A00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00999999"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -92,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,7 +120,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -501,7 +528,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +548,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -571,14 +598,2942 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>664.66</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>657.08</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>mean_reversion</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>supertrend_rsi</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>-38.22</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>-48.12</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>-48.12</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>-76.47</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>-218.67</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>-326.63</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>-348.48</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>-688.8099999999999</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>-1064.56</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>-1192.1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>-1623.78</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>-1626.69</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>-1862.55</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>-2601.44</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>-2810.63</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>-2914.38</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>-3537.16</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>-4114.42</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>-4322.28</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>-4394.7</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>-4468.55</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>-4507.14</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>-5109.59</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>-5208.86</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>-5950.03</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>-6485.55</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>-6626.43</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>-6943.41</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>-6978.65</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0.09519999999999999</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>-7101.28</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>rsi_psar_reversal</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>-7212.62</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>ema_price_action</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>-7374.71</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0.09300000000000001</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>-7482.56</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>-7745.5</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>-7877.31</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>-7894.67</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>-8039.42</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>-8333.540000000001</v>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>-8353.41</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>combo_trend_vwap</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>-8369.77</v>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>-8453.33</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>-8709.98</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>-8890.690000000001</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>-9350.58</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>-9376.85</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>-9657.860000000001</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>trendline_rsi</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H64" s="11" t="n">
+        <v>-9657.950000000001</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>-9730.66</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>-9743.610000000001</v>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>-9777.4</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>-9781.99</v>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H69" s="11" t="n">
+        <v>-9807.25</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>trend_pullback</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>-9815.629999999999</v>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H71" s="11" t="n">
+        <v>-9820.02</v>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>-9912.620000000001</v>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>-9968.24</v>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>opening_range_breakout</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>-9980.309999999999</v>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/13</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>-10051.53</v>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/13</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>-10051.53</v>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/21</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/26</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/21</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>EMA8/26</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/21</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H81" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>EMA9/26</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>-10066.88</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>rsi_adx_nw</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>EMA5/13</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H83" s="11" t="n">
+        <v>-10114.43</v>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
           <t>Note: small sample sizes (1-4 trades) don't prove a real edge yet. Grey rows = zero trades. Click the filter arrows on the header row to sort/filter.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A8:I83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>